--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Citt_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Citt_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="130">
   <si>
     <t>Sezione</t>
   </si>
@@ -119,6 +119,12 @@
     <t>descrizioneMotivoRecupero</t>
   </si>
   <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
+  </si>
+  <si>
     <t>Intestatario</t>
   </si>
   <si>
@@ -303,6 +309,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto collegato</t>
@@ -448,11 +460,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="22.48828125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="26.12109375" customWidth="true" bestFit="true"/>
@@ -738,19 +750,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -761,16 +773,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>40</v>
@@ -784,16 +796,16 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -807,16 +819,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -830,7 +842,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
@@ -839,7 +851,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -853,7 +865,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
@@ -862,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -876,7 +888,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
@@ -885,7 +897,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -899,16 +911,16 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -922,7 +934,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
@@ -931,7 +943,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -945,7 +957,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
@@ -954,7 +966,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -968,7 +980,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
@@ -977,7 +989,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -991,7 +1003,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>59</v>
@@ -1000,7 +1012,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>60</v>
@@ -1014,7 +1026,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>61</v>
@@ -1023,7 +1035,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>62</v>
@@ -1037,7 +1049,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
@@ -1046,7 +1058,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>64</v>
@@ -1060,7 +1072,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
@@ -1069,7 +1081,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>66</v>
@@ -1083,7 +1095,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
@@ -1092,7 +1104,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>68</v>
@@ -1106,7 +1118,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>69</v>
@@ -1115,7 +1127,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>70</v>
@@ -1129,7 +1141,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
@@ -1138,7 +1150,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>72</v>
@@ -1152,7 +1164,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>73</v>
@@ -1161,7 +1173,7 @@
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>74</v>
@@ -1175,7 +1187,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>75</v>
@@ -1184,7 +1196,7 @@
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>76</v>
@@ -1198,7 +1210,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>77</v>
@@ -1207,7 +1219,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>78</v>
@@ -1221,7 +1233,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>79</v>
@@ -1230,7 +1242,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>80</v>
@@ -1244,7 +1256,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>81</v>
@@ -1253,7 +1265,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>82</v>
@@ -1267,16 +1279,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>84</v>
@@ -1290,7 +1302,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>85</v>
@@ -1299,7 +1311,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>86</v>
@@ -1313,16 +1325,16 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>88</v>
@@ -1336,7 +1348,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>89</v>
@@ -1345,7 +1357,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>90</v>
@@ -1359,7 +1371,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>91</v>
@@ -1368,7 +1380,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>92</v>
@@ -1382,7 +1394,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>93</v>
@@ -1391,7 +1403,7 @@
         <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>94</v>
@@ -1405,7 +1417,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>95</v>
@@ -1414,7 +1426,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>96</v>
@@ -1428,76 +1440,76 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="F45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>106</v>
@@ -1506,7 +1518,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>107</v>
@@ -1515,12 +1527,12 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>108</v>
@@ -1529,7 +1541,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>109</v>
@@ -1538,12 +1550,12 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>110</v>
@@ -1552,7 +1564,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>111</v>
@@ -1561,12 +1573,12 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>112</v>
@@ -1575,113 +1587,113 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>120</v>
@@ -1690,7 +1702,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>121</v>
@@ -1699,12 +1711,12 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>122</v>
@@ -1713,7 +1725,7 @@
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>123</v>
@@ -1722,21 +1734,21 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>125</v>
@@ -1745,6 +1757,52 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Citt_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Citt_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="136">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -472,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -531,63 +537,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -596,90 +602,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -688,21 +694,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -711,21 +717,21 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -734,21 +740,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -757,21 +763,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -780,44 +786,44 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -826,21 +832,21 @@
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -849,12 +855,12 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
@@ -863,7 +869,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -872,21 +878,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -895,21 +901,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -918,12 +924,12 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
@@ -932,7 +938,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -941,21 +947,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -964,21 +970,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -987,21 +993,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -1010,21 +1016,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>60</v>
@@ -1033,21 +1039,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>62</v>
@@ -1056,21 +1062,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>64</v>
@@ -1079,21 +1085,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>66</v>
@@ -1102,21 +1108,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>68</v>
@@ -1125,21 +1131,21 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>70</v>
@@ -1148,21 +1154,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>72</v>
@@ -1171,21 +1177,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>74</v>
@@ -1194,21 +1200,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>76</v>
@@ -1217,21 +1223,21 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>78</v>
@@ -1240,21 +1246,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>80</v>
@@ -1263,21 +1269,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>82</v>
@@ -1286,21 +1292,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>84</v>
@@ -1309,21 +1315,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>86</v>
@@ -1332,21 +1338,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>88</v>
@@ -1355,12 +1361,12 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>89</v>
@@ -1369,7 +1375,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>90</v>
@@ -1378,21 +1384,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>92</v>
@@ -1401,21 +1407,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>94</v>
@@ -1424,21 +1430,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>96</v>
@@ -1447,21 +1453,21 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>98</v>
@@ -1470,21 +1476,21 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>100</v>
@@ -1493,21 +1499,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>102</v>
@@ -1516,21 +1522,21 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>104</v>
@@ -1539,67 +1545,67 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E48" s="2" t="s">
+      <c r="F48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>113</v>
@@ -1608,21 +1614,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>115</v>
@@ -1631,21 +1637,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>117</v>
@@ -1654,21 +1660,21 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>119</v>
@@ -1677,113 +1683,113 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>127</v>
@@ -1792,21 +1798,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>129</v>
@@ -1815,21 +1821,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>131</v>
@@ -1838,12 +1844,12 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>132</v>
@@ -1852,7 +1858,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>133</v>
@@ -1861,7 +1867,30 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>16</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
